--- a/branches/docs/su-termserv-production-setup/StructureDefinition-example-patient.xlsx
+++ b/branches/docs/su-termserv-production-setup/StructureDefinition-example-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T09:01:26+00:00</t>
+    <t>2026-07-26T09:04:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
